--- a/outputs/excel/bracket_pronostics.xlsx
+++ b/outputs/excel/bracket_pronostics.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="40">
   <si>
     <t>seed</t>
   </si>
@@ -35,28 +35,52 @@
     <t>inactivity</t>
   </si>
   <si>
-    <t>BONTHOUX Julien</t>
-  </si>
-  <si>
-    <t>PINEL Florian</t>
+    <t>LANDEMAINE Thierry</t>
+  </si>
+  <si>
+    <t>BAKAYOKO Ahmed</t>
+  </si>
+  <si>
+    <t>DUBOIS Constance</t>
+  </si>
+  <si>
+    <t>BLAYE Arnaud</t>
+  </si>
+  <si>
+    <t>LOUIS-JOSEPH Fernand</t>
+  </si>
+  <si>
+    <t>LECARPENTIER Stéphane</t>
+  </si>
+  <si>
+    <t>BARBET Catherine</t>
+  </si>
+  <si>
+    <t>SAADA Gilbert</t>
+  </si>
+  <si>
+    <t>DINOMAIS Hervé</t>
+  </si>
+  <si>
+    <t>DURAND Catherine</t>
+  </si>
+  <si>
+    <t>BOSSER Vincent</t>
+  </si>
+  <si>
+    <t>LEROUX Brigitte</t>
+  </si>
+  <si>
+    <t>BUNOUF Corentin</t>
   </si>
   <si>
     <t>CHASSARD Alexandre</t>
   </si>
   <si>
-    <t>DUMAS Geneviève</t>
-  </si>
-  <si>
-    <t>TULIN Steve</t>
-  </si>
-  <si>
-    <t>SCHAFTER Olivier</t>
-  </si>
-  <si>
-    <t>CHASSIGNOL Édith</t>
-  </si>
-  <si>
-    <t>PERRIN Marcel</t>
+    <t>JUSTET Myriam</t>
+  </si>
+  <si>
+    <t>KOUDJONOU Koffi</t>
   </si>
   <si>
     <t>elo_original</t>
@@ -71,7 +95,7 @@
     <t>manual_override</t>
   </si>
   <si>
-    <t>match_qf</t>
+    <t>match_r16</t>
   </si>
   <si>
     <t>seed_a</t>
@@ -99,6 +123,9 @@
   </si>
   <si>
     <t>Top8</t>
+  </si>
+  <si>
+    <t>elim_R16</t>
   </si>
   <si>
     <t>elim_QF</t>
@@ -474,11 +501,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
@@ -509,13 +536,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>1829</v>
+        <v>2097</v>
       </c>
       <c r="D2">
-        <v>138</v>
+        <v>431</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -526,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>2011</v>
+        <v>1870</v>
       </c>
       <c r="D3">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -543,13 +570,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="D4">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -560,13 +587,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>1616</v>
+        <v>2155</v>
       </c>
       <c r="D5">
-        <v>245</v>
+        <v>526</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -577,13 +604,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>1500</v>
+        <v>1673</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -594,13 +621,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>1721</v>
+        <v>1630</v>
       </c>
       <c r="D7">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -611,13 +638,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>1631</v>
+        <v>1796</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>363</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -628,13 +655,149 @@
         <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>1595</v>
+        <v>1757</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="E9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1738</v>
+      </c>
+      <c r="D10">
+        <v>166</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1598</v>
+      </c>
+      <c r="D11">
+        <v>241</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1596</v>
+      </c>
+      <c r="D12">
+        <v>123</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1586</v>
+      </c>
+      <c r="D13">
+        <v>79</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1460</v>
+      </c>
+      <c r="D14">
+        <v>187</v>
+      </c>
+      <c r="E14">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1695</v>
+      </c>
+      <c r="D15">
+        <v>197</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1564</v>
+      </c>
+      <c r="D16">
+        <v>83</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1585</v>
+      </c>
+      <c r="D17">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -644,11 +807,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
@@ -665,16 +828,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
@@ -691,19 +854,19 @@
         <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>1829</v>
+        <v>2097</v>
       </c>
       <c r="E2" s="1">
-        <v>1829</v>
+        <v>2097</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>138</v>
+        <v>431</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -714,19 +877,19 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>2011</v>
+        <v>1870</v>
       </c>
       <c r="E3" s="1">
-        <v>2011</v>
+        <v>1870</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -737,19 +900,19 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="E4" s="1">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -760,19 +923,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>1616</v>
+        <v>2155</v>
       </c>
       <c r="E5" s="1">
-        <v>1616</v>
+        <v>2155</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>245</v>
+        <v>526</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -783,19 +946,19 @@
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>1500</v>
+        <v>1673</v>
       </c>
       <c r="E6" s="1">
-        <v>1500</v>
+        <v>1673</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -806,19 +969,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>1721</v>
+        <v>1630</v>
       </c>
       <c r="E7" s="1">
-        <v>1721</v>
+        <v>1630</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -829,19 +992,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>1631</v>
+        <v>1796</v>
       </c>
       <c r="E8" s="1">
-        <v>1631</v>
+        <v>1796</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>70</v>
+        <v>363</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -852,19 +1015,203 @@
         <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>1595</v>
+        <v>1757</v>
       </c>
       <c r="E9" s="1">
-        <v>1595</v>
+        <v>1757</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="H9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1738</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1738</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>166</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1598</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1598</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>241</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1596</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1596</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>123</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1586</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1586</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>79</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1460</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1460</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>187</v>
+      </c>
+      <c r="H14">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1695</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1695</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>197</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1564</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1564</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>83</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1585</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1585</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>29</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -874,31 +1221,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -912,10 +1259,10 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -923,16 +1270,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -940,16 +1287,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -957,16 +1304,84 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D5">
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -976,20 +1391,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="22.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" style="3" customWidth="1"/>
-    <col min="8" max="9" width="21.7109375" style="3" customWidth="1"/>
-    <col min="10" max="11" width="22.7109375" style="3" customWidth="1"/>
+    <col min="7" max="10" width="22.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="24.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -997,69 +1413,75 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>38</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>2011</v>
+        <v>2155</v>
       </c>
       <c r="D2" s="3">
-        <v>0.6137760115136323</v>
+        <v>0.4764298097636128</v>
       </c>
       <c r="E2" s="3">
-        <v>0.7634104800871935</v>
+        <v>0.5621251983671168</v>
       </c>
       <c r="F2" s="3">
-        <v>0.8991173716432768</v>
+        <v>0.87831996021173</v>
       </c>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>0.9608565972483071</v>
       </c>
       <c r="H2" s="3">
-        <v>0.1008826283567232</v>
+        <v>0.03914340275169292</v>
       </c>
       <c r="I2" s="3">
-        <v>0.1357068915560833</v>
+        <v>0.0825366370365771</v>
       </c>
       <c r="J2" s="3">
-        <v>0.1496344685735612</v>
+        <v>0.3161947618446131</v>
       </c>
       <c r="K2" s="3">
-        <v>0.6137760115136323</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>0.08569538860350406</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.4764298097636128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1067,241 +1489,566 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>1829</v>
+        <v>2097</v>
       </c>
       <c r="D3" s="3">
-        <v>0.2294509468016213</v>
+        <v>0.3021025118817277</v>
       </c>
       <c r="E3" s="3">
-        <v>0.6394389715353033</v>
+        <v>0.3726215288307492</v>
       </c>
       <c r="F3" s="3">
-        <v>0.7936407431881689</v>
+        <v>0.7609817422889887</v>
       </c>
       <c r="G3" s="3">
-        <v>1</v>
+        <v>0.9135559418806044</v>
       </c>
       <c r="H3" s="3">
-        <v>0.2063592568118311</v>
+        <v>0.08644405811939559</v>
       </c>
       <c r="I3" s="3">
-        <v>0.1542017716528656</v>
+        <v>0.1525741995916157</v>
       </c>
       <c r="J3" s="3">
-        <v>0.409988024733682</v>
+        <v>0.3883602134582395</v>
       </c>
       <c r="K3" s="3">
-        <v>0.2294509468016213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>0.07051901694902152</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.3021025118817277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="1">
+        <v>1870</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.09581022113486254</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.368052657602468</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.5141714394393482</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.8036369036378818</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.1963630963621182</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.2894654641985336</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.1461187818368802</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.2722424364676054</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.09581022113486254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1796</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.04489203162748973</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.2200555675154968</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.3425323088373874</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.7133732025211301</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.2866267974788699</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.3708408936837427</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.1224767413218906</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.175163535888007</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.04489203162748973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1709</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.01859524055394329</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.123811879812774</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.3133544533295846</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.5161125148126701</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.4838874851873299</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.2027580614830854</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.1895425735168106</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.1052166392588307</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.01859524055394329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1695</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.01554928433603331</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.1089535263551265</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.2863098604633065</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.48388748518733</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.51611251481267</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.1975776247240235</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.17735633410818</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.09340424201909314</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.01554928433603331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1757</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.01103007248803994</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.02261230062229483</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1134421880624357</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.5218606131992322</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.4781393868007678</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.4084184251367964</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.09082988744014089</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.01158222813425489</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.01103007248803994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1738</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.008593172242978935</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.01839926982957911</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.09784129823658805</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.4781393868007678</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.5218606131992322</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.3802980885641798</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.07944202840700894</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.009806097586600171</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.008593172242978935</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1">
-        <v>1721</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.05115457080976652</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.109375157624509</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.5316182978281073</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.4683817021718927</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.4222431402035984</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.05822058681474244</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.05115457080976652</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1699</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.03874189367260876</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.08813393388286619</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.4683817021718927</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.5316182978281072</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.3802477682890265</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.04939204021025743</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0.03874189367260876</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1616</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.03105584146813545</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.1913287810681292</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.6609990912463583</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.3390009087536417</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.4696703101782291</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.1602729395999937</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.03105584146813545</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C10" s="1">
+        <v>1630</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.007964478733391702</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.07114563664817386</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.2251273243959442</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.5390641711450747</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.4609358288549253</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.3139368467491305</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.1539816877477703</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.06318115791478215</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.007964478733391702</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1673</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.005798937002479101</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.01459494756037277</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.07343538172400496</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.5988437730133997</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.4011562269866003</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.5254083912893948</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.05884043416363219</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.008796010557893672</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.005798937002479101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1596</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.004900849224785375</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.04988612632920204</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.1752083618111649</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.4609358288549254</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.5390641711450745</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.2857274670437605</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.1253222354819629</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.04498527710441666</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.004900849224785375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1598</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.003402262855053968</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.03436465588865072</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.08153387368983632</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.2866267974788699</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.7133732025211301</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.2050929237890335</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.0471692178011856</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.03096239303359676</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.003402262855053968</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1564</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.002057315846116569</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.02372994984810833</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.06176237803342808</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.1963630963621182</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.8036369036378819</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.1346007183286901</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.03803242818531975</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.02167263400199176</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.002057315846116569</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
-        <v>1595</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.01607116426020332</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.108395004820275</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.2063592568118311</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.7936407431881689</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.09796425199155608</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.09232384056007173</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0.01607116426020332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1631</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.01391004572232357</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.03908042840543149</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.1008826283567233</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.8991173716432767</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.06180219995129185</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.02517038268310792</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0.01391004572232357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1500</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.005839525751709017</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.06083724257629258</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.3390009087536417</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.6609990912463583</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.2781636661773492</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.05499771682458356</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.005839525751709017</v>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1586</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.001662571610359187</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.005356410827705457</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.03621677842327489</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.4011562269866003</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.5988437730133997</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.3649394485633254</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.03086036759556943</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.00369383921734627</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.001662571610359187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1585</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.0009824697902183711</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.003174902261943401</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.02773477141198742</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.08644405811939565</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.9135559418806043</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.05870928670740823</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.02455986915004402</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.00219243247172503</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.0009824697902183711</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1460</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.0002287709089077473</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.001115441700238455</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.01202787964099028</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.03914340275169299</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.960856597248307</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.02711552311070271</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.01091243794075182</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.0008866707913307078</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.0002287709089077473</v>
       </c>
     </row>
   </sheetData>
@@ -1311,18 +2058,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
-    <col min="6" max="9" width="21.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="5" width="21.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="3" customWidth="1"/>
+    <col min="10" max="11" width="21.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" style="3" customWidth="1"/>
+    <col min="14" max="17" width="21.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1330,233 +2081,849 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="Q1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>0.7936407431881689</v>
+        <v>0.9135559418806044</v>
       </c>
       <c r="D2" s="3">
-        <v>0.7731399130767673</v>
+        <v>0.8271780169631395</v>
       </c>
       <c r="E2" s="3">
-        <v>0.8691968654550538</v>
+        <v>0.8393306357469655</v>
       </c>
       <c r="F2" s="3">
-        <v>0.2596715804851696</v>
+        <v>0.8757290153768147</v>
       </c>
       <c r="G2" s="3">
-        <v>0.7576391748622517</v>
+        <v>0.9131915714639824</v>
       </c>
       <c r="H2" s="3">
-        <v>0.6788169197947567</v>
+        <v>0.4336192105911411</v>
       </c>
       <c r="I2" s="3">
-        <v>0.6506046279338725</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>0.9494775171154728</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.8565352401453031</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.8642771336655589</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.8957261834608686</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.9094707853354177</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.7999778974620979</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0.9087095988243511</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0.7398855204796612</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.9208939633600981</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.08644405811939565</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.3117202383485725</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.3307951226552328</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.400050432677456</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.4988487094881773</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.06755002899657621</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.6400649998028851</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.3609966304745664</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.3759982413823328</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.4483764526890395</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.4873384894509742</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.2745435964565499</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.4850376654828339</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0.2120732319225979</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.5241583179244865</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.2063592568118311</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.469815319996098</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.6334077000711676</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.08357862293048655</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.4483764526890395</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.3546475495606176</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.3262238121116778</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+      <c r="B4" s="3">
+        <v>0.1728219830368604</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.6882797616514276</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.5218606131992322</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.5955203886984292</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.6872908633331829</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.1378981875575567</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.7970140504562645</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.5550381171426981</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.5708991378309802</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.6421841457808728</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.677309003222508</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.4552198977295314</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.6752926987298703</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.3727623920145446</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.7086420278758863</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.1606693642530344</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.6692048773447672</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.4781393868007678</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.5742802036545245</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.6681846389742985</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.1278218765719027</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.7824901694178099</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.5333379484196868</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.5493444401521689</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.6218383401921134</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.657896469648991</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.4336192105911411</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.655820505912395</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0.352542387570748</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.6902524121551514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.1242709846231852</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.599949567322544</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.4044796113015708</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.4257197963454756</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.5988437730133997</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.09799602329020159</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.7272870073571547</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.4586481380987735</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.4746932070195414</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.5493444401521689</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.5877321613612969</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.3620596207918618</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.5854986786718095</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0.2875693497730312</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.6229206617275551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.08680842853601746</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.5011512905118227</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.312709136666817</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.3318153610257015</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.4011562269866003</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.06784067326111998</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.6411252614133421</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.3620596207918618</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.3770793382724449</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.449515741335684</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.4884891087822083</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.275461757157464</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.486188004293249</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.2128437677935133</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.5253067929804586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.2268600869232327</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.5301846800039021</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B8" s="3">
+        <v>0.5663807894088588</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.9324499710034239</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.8621018124424432</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8721781234280973</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.9020039767097984</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.9321593267388801</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.9608565972483071</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.8863416939202873</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.8926766600061541</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.9181681752448481</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.9291884951489859</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.8393306357469655</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.9285800794640444</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.7879267680774021</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.9382924609335543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.0505224828845272</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.3599350001971149</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.2029859495437355</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.21750983058219</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.2727129926428454</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.3588747385866579</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.03914340275169299</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.2410946673404092</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.2530870785710568</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.3136997423166875</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.3483492602467557</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0.1754711945430433</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.3462614250257082</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0.1314590000241483</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.3825030034188878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.1434647598546969</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.6390033695254337</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.4449618828573019</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.4666620515803132</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.5413518619012265</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.6379403792081383</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.1136583060797127</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.7589053326595907</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.5161125148126701</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.5899620374901279</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.6272376079854555</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0.4011562269866003</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.6250816214956094</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0.322690996777492</v>
+      </c>
+      <c r="Q10" s="3">
         <v>0.6609990912463583</v>
       </c>
-      <c r="F4" s="3">
-        <v>0.09331596833848053</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.4784266669488546</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.3827749690950537</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.3533311576743853</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.1308031345449462</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.3665922999288324</v>
-      </c>
-      <c r="D5" s="3">
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.1357228663344411</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.6240017586176672</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.4291008621690198</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.4506555598478311</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.5253067929804586</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.6229206617275551</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.1073233399938459</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.7469129214289432</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.48388748518733</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.5742802036545245</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.6120439060166588</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.3857714039631269</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.6098547023340238</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.308763847585237</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.6464057411077517</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1042738165391314</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.5516235473109605</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.3578158542191273</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.3781616598078867</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.4506555598478311</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.5504842586643161</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.08183182475515199</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.6863002576833125</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.4100379625098722</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.4257197963454756</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.5390641711450747</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.3176791152567424</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.536774833611817</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0.2487592064662893</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.5754056999594935</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.09052921466458225</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.5126615105490258</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.322690996777492</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.3421035303510091</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.4122678386387032</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.5115108912177917</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.07081150485101413</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.6516507397532443</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.3727623920145446</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.3879560939833412</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.4609358288549254</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.2847472489508014</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.4976974311842966</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.2206613278377197</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.536774833611817</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.200022102537902</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.7254564035434501</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.5447801022704686</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.5663807894088588</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.6379403792081383</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.7245382428425361</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.1606693642530344</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.8245288054569567</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.5988437730133997</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.6142285960368731</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.6823208847432576</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.7152527510491987</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.7133732025211301</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.4156193882170406</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.7442924226402794</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.09129040117564889</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.514962334517166</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.3247073012701297</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.344179494087605</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.4145013213281905</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.513811995706751</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.07141992053595553</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.6537385749742918</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.3749183785043906</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.3901452976659761</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.463225166388183</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.5023025688157033</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.2866267974788699</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0.222249303532796</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.5390641711450747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.2601144795203388</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.7879267680774021</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.6272376079854555</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.6474576124292521</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.7124306502269688</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.7871562322064868</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.2120732319225979</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.8685409999758518</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.677309003222508</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.691236152414763</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.7512407935337106</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.7793386721622803</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.5843806117829594</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.777750696467204</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.8036369036378818</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.07910603663990187</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.4758416820755134</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.2913579721241137</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.3097475878448485</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.3770793382724449</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.4746932070195414</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.06170753906644569</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.6174969965811122</v>
+      </c>
+      <c r="J17" s="3">
         <v>0.3390009087536417</v>
       </c>
-      <c r="F5" s="3">
-        <v>0.05013728806915506</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.3199293242627785</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.2413053798531443</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.2188845972700383</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.7403284195148304</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.9164213770695134</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.9066840316615196</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.949862711930845</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.8991173716432768</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.8576633185538569</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.8414923669232418</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.2423608251377483</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.5516235473109605</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.5215733330511455</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.6800706757372215</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.1008826283567233</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.403370826694226</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.373300918333268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.3211830802052434</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.6453524504393825</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.6172250309049463</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.7586946201468556</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.1423366814461431</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.596629173305774</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.4683817021718927</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.3493953720661275</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.6737761878883222</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.6466688423256146</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.7811154027299616</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.1585076330767582</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.626699081666732</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.5316182978281073</v>
+      <c r="K17" s="3">
+        <v>0.3535942588922482</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.4245943000405065</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.463225166388183</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.2557075773597206</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.4609358288549254</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.1963630963621182</v>
       </c>
     </row>
   </sheetData>
